--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13935C26-5A90-45F4-A5CE-38C3E21770FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA43A4B2-8104-4F71-9E77-D51D31D1C84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
   <si>
     <t>PAINEL FINANCEIRO E DE OCUPAÇÃO</t>
   </si>
@@ -386,6 +386,15 @@
   </si>
   <si>
     <t>Regina - 7 de Setembro</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>Cortesia</t>
+  </si>
+  <si>
+    <t>Louis Renan - Férias</t>
   </si>
 </sst>
 </file>
@@ -800,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -908,6 +917,16 @@
     <xf numFmtId="166" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -919,20 +938,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1262,22 +1267,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
+      <c r="A1" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
     </row>
     <row r="3" spans="1:14" ht="22.8">
       <c r="A3" s="1" t="s">
@@ -1286,10 +1291,10 @@
       <c r="B3" s="7">
         <v>2026</v>
       </c>
-      <c r="M3" s="90" t="s">
+      <c r="M3" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="89">
+      <c r="N3" s="85">
         <f>SUMIFS(RESERVAS!$Y$6:$Y$205,RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")</f>
         <v>13800</v>
       </c>
@@ -1319,7 +1324,7 @@
       <c r="J5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="95">
+      <c r="K5" s="91">
         <f>SUM(I13:I24)</f>
         <v>10500</v>
       </c>
@@ -1330,7 +1335,7 @@
       </c>
       <c r="B8" s="12">
         <f>SUM(C13:C24)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="74" t="s">
@@ -1338,21 +1343,21 @@
       </c>
       <c r="E8" s="12">
         <f>SUM(D13:D24)</f>
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="13">
         <f>IF(SUM(B13:B24)=0,0,SUM(C13:C24)/SUM(B13:B24))</f>
-        <v>3.0136986301369864E-2</v>
+        <v>5.2054794520547946E-2</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="10">
         <f>IF(B8=0,0,B5/B8)</f>
-        <v>954.5454545454545</v>
+        <v>552.63157894736844</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1">
@@ -1386,11 +1391,11 @@
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="87" t="s">
+      <c r="L12" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="87"/>
-      <c r="N12" s="87"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="95"/>
     </row>
     <row r="13" spans="1:14" ht="17.399999999999999">
       <c r="A13" s="15" t="s">
@@ -1400,11 +1405,11 @@
         <f>DAY(EOMONTH(DATE($B$3,1,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C13" s="93">
+      <c r="C13" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,2,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,1,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,2,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,2,1))*DATE($B$3,2,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,1,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,1,1))*DATE($B$3,1,1))))</f>
         <v>0</v>
       </c>
-      <c r="D13" s="93">
+      <c r="D13" s="89">
         <f t="shared" ref="D13:D24" si="0">MAX(0,B13-C13)</f>
         <v>31</v>
       </c>
@@ -1424,7 +1429,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,1,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,2,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="91">
+      <c r="I13" s="87">
         <f t="shared" ref="I13:I24" si="2">F13-G13-H13</f>
         <v>0</v>
       </c>
@@ -1448,11 +1453,11 @@
         <f>DAY(EOMONTH(DATE($B$3,2,1),0))</f>
         <v>28</v>
       </c>
-      <c r="C14" s="93">
+      <c r="C14" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,3,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,2,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,3,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,3,1))*DATE($B$3,3,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,2,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,2,1))*DATE($B$3,2,1))))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="93">
+      <c r="D14" s="89">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -1472,7 +1477,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,2,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,3,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="91">
+      <c r="I14" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1496,11 +1501,11 @@
         <f>DAY(EOMONTH(DATE($B$3,3,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C15" s="93">
+      <c r="C15" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,4,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,3,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,4,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,4,1))*DATE($B$3,4,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,3,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,3,1))*DATE($B$3,3,1))))</f>
         <v>0</v>
       </c>
-      <c r="D15" s="93">
+      <c r="D15" s="89">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -1520,7 +1525,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,3,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,4,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="91">
+      <c r="I15" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1544,11 +1549,11 @@
         <f>DAY(EOMONTH(DATE($B$3,4,1),0))</f>
         <v>30</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,5,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,4,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,5,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,5,1))*DATE($B$3,5,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,4,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,4,1))*DATE($B$3,4,1))))</f>
         <v>0</v>
       </c>
-      <c r="D16" s="93">
+      <c r="D16" s="89">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1568,7 +1573,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,4,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,5,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="91">
+      <c r="I16" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1592,11 +1597,11 @@
         <f>DAY(EOMONTH(DATE($B$3,5,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C17" s="93">
+      <c r="C17" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,6,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,5,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,6,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,6,1))*DATE($B$3,6,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,5,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,5,1))*DATE($B$3,5,1))))</f>
         <v>0</v>
       </c>
-      <c r="D17" s="93">
+      <c r="D17" s="89">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -1616,7 +1621,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,5,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,6,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="91">
+      <c r="I17" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1640,11 +1645,11 @@
         <f>DAY(EOMONTH(DATE($B$3,6,1),0))</f>
         <v>30</v>
       </c>
-      <c r="C18" s="93">
+      <c r="C18" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,7,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,6,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,7,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,7,1))*DATE($B$3,7,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,6,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,6,1))*DATE($B$3,6,1))))</f>
         <v>0</v>
       </c>
-      <c r="D18" s="93">
+      <c r="D18" s="89">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1664,7 +1669,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,6,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,7,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="91">
+      <c r="I18" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1681,11 +1686,11 @@
         <f>DAY(EOMONTH(DATE($B$3,7,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C19" s="93">
+      <c r="C19" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,8,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,7,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,8,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,8,1))*DATE($B$3,8,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,7,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,7,1))*DATE($B$3,7,1))))</f>
         <v>0</v>
       </c>
-      <c r="D19" s="93">
+      <c r="D19" s="89">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -1705,7 +1710,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,7,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,8,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="91">
+      <c r="I19" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1722,17 +1727,17 @@
         <f>DAY(EOMONTH(DATE($B$3,8,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C20" s="93">
+      <c r="C20" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,9,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,8,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,9,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,9,1))*DATE($B$3,9,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,8,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,8,1))*DATE($B$3,8,1))))</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="93">
+        <v>4</v>
+      </c>
+      <c r="D20" s="89">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="F20" s="5">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,9,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,8,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$205*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,9,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,9,1))*DATE($B$3,9,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,8,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,8,1))*DATE($B$3,8,1))))</f>
@@ -1746,7 +1751,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,8,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,9,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I20" s="91">
+      <c r="I20" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1763,17 +1768,17 @@
         <f>DAY(EOMONTH(DATE($B$3,9,1),0))</f>
         <v>30</v>
       </c>
-      <c r="C21" s="93">
+      <c r="C21" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,10,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,9,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,10,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,10,1))*DATE($B$3,10,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,9,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,9,1))*DATE($B$3,9,1))))</f>
-        <v>4</v>
-      </c>
-      <c r="D21" s="93">
+        <v>8</v>
+      </c>
+      <c r="D21" s="89">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="F21" s="5">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,10,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,9,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$205*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,10,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,10,1))*DATE($B$3,10,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,9,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,9,1))*DATE($B$3,9,1))))</f>
@@ -1787,7 +1792,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,9,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,10,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="91">
+      <c r="I21" s="87">
         <f t="shared" si="2"/>
         <v>2800</v>
       </c>
@@ -1804,11 +1809,11 @@
         <f>DAY(EOMONTH(DATE($B$3,10,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C22" s="93">
+      <c r="C22" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,11,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,10,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,11,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,11,1))*DATE($B$3,11,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,10,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,10,1))*DATE($B$3,10,1))))</f>
         <v>0</v>
       </c>
-      <c r="D22" s="93">
+      <c r="D22" s="89">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -1828,7 +1833,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,10,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,11,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I22" s="91">
+      <c r="I22" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1845,11 +1850,11 @@
         <f>DAY(EOMONTH(DATE($B$3,11,1),0))</f>
         <v>30</v>
       </c>
-      <c r="C23" s="93">
+      <c r="C23" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,12,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,11,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,12,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,12,1))*DATE($B$3,12,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,11,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,11,1))*DATE($B$3,11,1))))</f>
         <v>0</v>
       </c>
-      <c r="D23" s="93">
+      <c r="D23" s="89">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1869,7 +1874,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,11,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,12,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I23" s="91">
+      <c r="I23" s="87">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1886,11 +1891,11 @@
         <f>DAY(EOMONTH(DATE($B$3,12,1),0))</f>
         <v>31</v>
       </c>
-      <c r="C24" s="94">
+      <c r="C24" s="90">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($B$3,13,1))*(RESERVAS!$D$6:$D$205&gt;DATE($B$3,12,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($B$3,13,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($B$3,13,1))*DATE($B$3,13,1))-((RESERVAS!$C$6:$C$205&gt;DATE($B$3,12,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($B$3,12,1))*DATE($B$3,12,1))))</f>
         <v>7</v>
       </c>
-      <c r="D24" s="94">
+      <c r="D24" s="90">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -1910,7 +1915,7 @@
         <f>SUMIFS('DESPESAS CASA'!$D$6:$D$305,'DESPESAS CASA'!$A$6:$A$305,"&gt;="&amp;DATE($B$3,12,1),'DESPESAS CASA'!$A$6:$A$305,"&lt;"&amp;DATE($B$3,13,1),'DESPESAS CASA'!$E$6:$E$305,"")</f>
         <v>0</v>
       </c>
-      <c r="I24" s="92">
+      <c r="I24" s="88">
         <f t="shared" si="2"/>
         <v>7700</v>
       </c>
@@ -1978,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
@@ -1988,27 +1993,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1</v>
@@ -2021,7 +2026,7 @@
       </c>
       <c r="K2" s="28">
         <f>MATCH(B2,LISTAS!$A$4:$A$15,0)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="24" customHeight="1">
@@ -2046,12 +2051,12 @@
       <c r="G4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="88" t="s">
+      <c r="I4" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
     </row>
     <row r="5" spans="1:12" ht="60.75" customHeight="1">
       <c r="A5" s="29" t="str">
@@ -2076,31 +2081,35 @@
       <c r="E5" s="30" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+4))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>04
-DISPONÍVEL</v>
+ALUGADA
+Regina - 7 de Setembro</v>
       </c>
       <c r="F5" s="30" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+5))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>05
-DISPONÍVEL</v>
+ALUGADA
+Regina - 7 de Setembro</v>
       </c>
       <c r="G5" s="31" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+6))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>06
-DISPONÍVEL</v>
+ALUGADA
+Regina - 7 de Setembro</v>
       </c>
       <c r="I5" s="35" t="s">
         <v>16</v>
       </c>
       <c r="J5" s="36">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($E$2,$K$2+1,1))*(RESERVAS!$D$6:$D$205&gt;DATE($E$2,$K$2,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$205*(((RESERVAS!$D$6:$D$205&lt;DATE($E$2,$K$2+1,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($E$2,$K$2+1,1))*DATE($E$2,$K$2+1,1))-((RESERVAS!$C$6:$C$205&gt;DATE($E$2,$K$2,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($E$2,$K$2,1))*DATE($E$2,$K$2,1))))</f>
-        <v>7700</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="60.75" customHeight="1">
       <c r="A6" s="32" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+7))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>07
-DISPONÍVEL</v>
+ALUGADA
+Regina - 7 de Setembro</v>
       </c>
       <c r="B6" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+8))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
@@ -2198,63 +2207,59 @@
       <c r="C8" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+23))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>23
-DISPONÍVEL</v>
+ALUGADA
+Louis Renan - Férias</v>
       </c>
       <c r="D8" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+24))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>24
-DISPONÍVEL</v>
+ALUGADA
+Louis Renan - Férias</v>
       </c>
       <c r="E8" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+25))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>25
 ALUGADA
-Carlos - Natal/Ano Novo</v>
+Louis Renan - Férias</v>
       </c>
       <c r="F8" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>26
 ALUGADA
-Carlos - Natal/Ano Novo</v>
+Louis Renan - Férias</v>
       </c>
       <c r="G8" s="34" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>27
-ALUGADA
-Carlos - Natal/Ano Novo</v>
+DISPONÍVEL</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>6</v>
       </c>
       <c r="J8" s="36">
         <f>J5-J6-J7</f>
-        <v>7700</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="60.75" customHeight="1">
       <c r="A9" s="32" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+28))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>28
-ALUGADA
-Carlos - Natal/Ano Novo</v>
+DISPONÍVEL</v>
       </c>
       <c r="B9" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+29))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>29
-ALUGADA
-Carlos - Natal/Ano Novo</v>
+DISPONÍVEL</v>
       </c>
       <c r="C9" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+30))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v>30
-ALUGADA
-Carlos - Natal/Ano Novo</v>
+DISPONÍVEL</v>
       </c>
       <c r="D9" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+31))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
-        <v>31
-ALUGADA
-Carlos - Natal/Ano Novo</v>
+        <v/>
       </c>
       <c r="E9" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+32))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
@@ -2273,7 +2278,7 @@
       </c>
       <c r="J9" s="37">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$205&lt;DATE($E$2,$K$2+1,1))*(RESERVAS!$D$6:$D$205&gt;DATE($E$2,$K$2,1))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$205&lt;DATE($E$2,$K$2+1,1))*RESERVAS!$D$6:$D$205+(RESERVAS!$D$6:$D$205&gt;=DATE($E$2,$K$2+1,1))*DATE($E$2,$K$2+1,1))-((RESERVAS!$C$6:$C$205&gt;DATE($E$2,$K$2,1))*RESERVAS!$C$6:$C$205+(RESERVAS!$C$6:$C$205&lt;=DATE($E$2,$K$2,1))*DATE($E$2,$K$2,1))))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="60.75" customHeight="1">
@@ -2281,23 +2286,23 @@
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+35))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v/>
       </c>
-      <c r="B10" s="96" t="str">
+      <c r="B10" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+36))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v/>
       </c>
-      <c r="C10" s="96" t="str">
+      <c r="C10" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+37))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v/>
       </c>
-      <c r="D10" s="96" t="str">
+      <c r="D10" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+38))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v/>
       </c>
-      <c r="E10" s="96" t="str">
+      <c r="E10" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+39))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v/>
       </c>
-      <c r="F10" s="96" t="str">
+      <c r="F10" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$205,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),RESERVAS!$D$6:$D$205,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40),RESERVAS!$I$6:$I$205,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$205,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$205&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40))*(RESERVAS!$D$6:$D$205&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+40))*(RESERVAS!$I$6:$I$205&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$205&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$205),"")))</f>
         <v/>
       </c>
@@ -2310,41 +2315,32 @@
       </c>
       <c r="J10" s="38">
         <f>IF(DAY(EOMONTH(DATE($E$2,$K$2,1),0))=0,0,J9/DAY(EOMONTH(DATE($E$2,$K$2,1),0)))</f>
-        <v>0.22580645161290322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="97"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
+        <v>0.26666666666666666</v>
+      </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="98"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="I12" s="87" t="s">
+      <c r="A12" s="92"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="I12" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="87"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="87"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="95"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="98"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
       <c r="I13" s="39" t="s">
         <v>49</v>
       </c>
@@ -2353,13 +2349,13 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="98"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
+      <c r="A14" s="92"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
       <c r="I14" s="40" t="s">
         <v>51</v>
       </c>
@@ -2368,82 +2364,12 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="97"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="97"/>
-      <c r="G15" s="97"/>
       <c r="I15" s="41" t="s">
         <v>53</v>
       </c>
       <c r="J15" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="97"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="97"/>
-      <c r="F16" s="97"/>
-      <c r="G16" s="97"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="97"/>
-      <c r="B17" s="97"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="97"/>
-      <c r="E17" s="97"/>
-      <c r="F17" s="97"/>
-      <c r="G17" s="97"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="97"/>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="97"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="97"/>
-      <c r="B19" s="97"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="97"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="97"/>
-      <c r="B21" s="97"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="97"/>
-      <c r="B22" s="97"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="97"/>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2503,66 +2429,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="24" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
+      <c r="U1" s="93"/>
+      <c r="V1" s="93"/>
+      <c r="W1" s="93"/>
+      <c r="X1" s="93"/>
+      <c r="Y1" s="93"/>
+      <c r="Z1" s="93"/>
+      <c r="AA1" s="93"/>
     </row>
     <row r="3" spans="1:27" ht="14.4">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86"/>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="86"/>
-      <c r="AA3" s="86"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="94"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="94"/>
+      <c r="V3" s="94"/>
+      <c r="W3" s="94"/>
+      <c r="X3" s="94"/>
+      <c r="Y3" s="94"/>
+      <c r="Z3" s="94"/>
+      <c r="AA3" s="94"/>
     </row>
     <row r="5" spans="1:27" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -2771,7 +2697,7 @@
       <c r="I7" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="54" t="s">
         <v>99</v>
       </c>
       <c r="K7" s="47"/>
@@ -2816,23 +2742,37 @@
     <row r="8" spans="1:27">
       <c r="A8" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
+        <v>LOC-003</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="45">
+        <v>46257</v>
+      </c>
+      <c r="D8" s="45">
+        <v>46261</v>
+      </c>
       <c r="E8" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="47"/>
+        <v>4</v>
+      </c>
+      <c r="F8" s="47">
+        <v>0</v>
+      </c>
       <c r="G8" s="51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
+      <c r="H8" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="54" t="s">
+        <v>118</v>
+      </c>
       <c r="K8" s="47"/>
       <c r="L8" s="47"/>
       <c r="M8" s="47"/>
@@ -2868,30 +2808,44 @@
       </c>
       <c r="Z8" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA8" s="63"/>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+        <v>LOC-004</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="45">
+        <v>46288</v>
+      </c>
+      <c r="D9" s="45">
+        <v>46292</v>
+      </c>
       <c r="E9" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="47"/>
+        <v>4</v>
+      </c>
+      <c r="F9" s="47">
+        <v>0</v>
+      </c>
       <c r="G9" s="51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
+      <c r="H9" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>118</v>
+      </c>
       <c r="K9" s="47"/>
       <c r="L9" s="47"/>
       <c r="M9" s="47"/>
@@ -2927,7 +2881,7 @@
       </c>
       <c r="Z9" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA9" s="63"/>
     </row>
@@ -2950,7 +2904,7 @@
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
       <c r="M10" s="47"/>
@@ -3009,7 +2963,7 @@
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="47"/>
       <c r="L11" s="47"/>
       <c r="M11" s="47"/>
@@ -3068,7 +3022,7 @@
       </c>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
       <c r="M12" s="47"/>
@@ -3127,7 +3081,7 @@
       </c>
       <c r="H13" s="43"/>
       <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="47"/>
       <c r="L13" s="47"/>
       <c r="M13" s="47"/>
@@ -3186,7 +3140,7 @@
       </c>
       <c r="H14" s="43"/>
       <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="47"/>
       <c r="L14" s="47"/>
       <c r="M14" s="47"/>
@@ -3245,7 +3199,7 @@
       </c>
       <c r="H15" s="43"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="47"/>
       <c r="L15" s="47"/>
       <c r="M15" s="47"/>
@@ -3304,7 +3258,7 @@
       </c>
       <c r="H16" s="43"/>
       <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="47"/>
       <c r="L16" s="47"/>
       <c r="M16" s="47"/>
@@ -3363,7 +3317,7 @@
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="47"/>
       <c r="L17" s="47"/>
       <c r="M17" s="47"/>
@@ -3422,7 +3376,7 @@
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="47"/>
       <c r="L18" s="47"/>
       <c r="M18" s="47"/>
@@ -3481,7 +3435,7 @@
       </c>
       <c r="H19" s="43"/>
       <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="47"/>
       <c r="L19" s="47"/>
       <c r="M19" s="47"/>
@@ -3540,7 +3494,7 @@
       </c>
       <c r="H20" s="43"/>
       <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="47"/>
       <c r="L20" s="47"/>
       <c r="M20" s="47"/>
@@ -3599,7 +3553,7 @@
       </c>
       <c r="H21" s="43"/>
       <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="47"/>
       <c r="L21" s="47"/>
       <c r="M21" s="47"/>
@@ -3658,7 +3612,7 @@
       </c>
       <c r="H22" s="43"/>
       <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
       <c r="M22" s="47"/>
@@ -3717,7 +3671,7 @@
       </c>
       <c r="H23" s="43"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
+      <c r="J23" s="54"/>
       <c r="K23" s="47"/>
       <c r="L23" s="47"/>
       <c r="M23" s="47"/>
@@ -3776,7 +3730,7 @@
       </c>
       <c r="H24" s="43"/>
       <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
+      <c r="J24" s="54"/>
       <c r="K24" s="47"/>
       <c r="L24" s="47"/>
       <c r="M24" s="47"/>
@@ -3835,7 +3789,7 @@
       </c>
       <c r="H25" s="43"/>
       <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
+      <c r="J25" s="54"/>
       <c r="K25" s="47"/>
       <c r="L25" s="47"/>
       <c r="M25" s="47"/>
@@ -3894,7 +3848,7 @@
       </c>
       <c r="H26" s="43"/>
       <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
+      <c r="J26" s="54"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
       <c r="M26" s="47"/>
@@ -3953,7 +3907,7 @@
       </c>
       <c r="H27" s="43"/>
       <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="47"/>
       <c r="L27" s="47"/>
       <c r="M27" s="47"/>
@@ -4012,7 +3966,7 @@
       </c>
       <c r="H28" s="43"/>
       <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="47"/>
       <c r="L28" s="47"/>
       <c r="M28" s="47"/>
@@ -4071,7 +4025,7 @@
       </c>
       <c r="H29" s="43"/>
       <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="47"/>
       <c r="L29" s="47"/>
       <c r="M29" s="47"/>
@@ -4130,7 +4084,7 @@
       </c>
       <c r="H30" s="43"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="47"/>
       <c r="L30" s="47"/>
       <c r="M30" s="47"/>
@@ -4189,7 +4143,7 @@
       </c>
       <c r="H31" s="43"/>
       <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
+      <c r="J31" s="54"/>
       <c r="K31" s="47"/>
       <c r="L31" s="47"/>
       <c r="M31" s="47"/>
@@ -4248,7 +4202,7 @@
       </c>
       <c r="H32" s="43"/>
       <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
+      <c r="J32" s="54"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
       <c r="M32" s="47"/>
@@ -4307,7 +4261,7 @@
       </c>
       <c r="H33" s="43"/>
       <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="47"/>
       <c r="L33" s="47"/>
       <c r="M33" s="47"/>
@@ -4366,7 +4320,7 @@
       </c>
       <c r="H34" s="43"/>
       <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="47"/>
       <c r="L34" s="47"/>
       <c r="M34" s="47"/>
@@ -4425,7 +4379,7 @@
       </c>
       <c r="H35" s="43"/>
       <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="47"/>
       <c r="L35" s="47"/>
       <c r="M35" s="47"/>
@@ -4484,7 +4438,7 @@
       </c>
       <c r="H36" s="43"/>
       <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="47"/>
       <c r="L36" s="47"/>
       <c r="M36" s="47"/>
@@ -4543,7 +4497,7 @@
       </c>
       <c r="H37" s="43"/>
       <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="47"/>
       <c r="L37" s="47"/>
       <c r="M37" s="47"/>
@@ -4602,7 +4556,7 @@
       </c>
       <c r="H38" s="43"/>
       <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
+      <c r="J38" s="54"/>
       <c r="K38" s="47"/>
       <c r="L38" s="47"/>
       <c r="M38" s="47"/>
@@ -4661,7 +4615,7 @@
       </c>
       <c r="H39" s="43"/>
       <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
+      <c r="J39" s="54"/>
       <c r="K39" s="47"/>
       <c r="L39" s="47"/>
       <c r="M39" s="47"/>
@@ -4720,7 +4674,7 @@
       </c>
       <c r="H40" s="43"/>
       <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
+      <c r="J40" s="54"/>
       <c r="K40" s="47"/>
       <c r="L40" s="47"/>
       <c r="M40" s="47"/>
@@ -4779,7 +4733,7 @@
       </c>
       <c r="H41" s="43"/>
       <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
+      <c r="J41" s="54"/>
       <c r="K41" s="47"/>
       <c r="L41" s="47"/>
       <c r="M41" s="47"/>
@@ -4838,7 +4792,7 @@
       </c>
       <c r="H42" s="43"/>
       <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
+      <c r="J42" s="54"/>
       <c r="K42" s="47"/>
       <c r="L42" s="47"/>
       <c r="M42" s="47"/>
@@ -4897,7 +4851,7 @@
       </c>
       <c r="H43" s="43"/>
       <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
+      <c r="J43" s="54"/>
       <c r="K43" s="47"/>
       <c r="L43" s="47"/>
       <c r="M43" s="47"/>
@@ -4956,7 +4910,7 @@
       </c>
       <c r="H44" s="43"/>
       <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
+      <c r="J44" s="54"/>
       <c r="K44" s="47"/>
       <c r="L44" s="47"/>
       <c r="M44" s="47"/>
@@ -5015,7 +4969,7 @@
       </c>
       <c r="H45" s="43"/>
       <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
+      <c r="J45" s="54"/>
       <c r="K45" s="47"/>
       <c r="L45" s="47"/>
       <c r="M45" s="47"/>
@@ -5074,7 +5028,7 @@
       </c>
       <c r="H46" s="43"/>
       <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
+      <c r="J46" s="54"/>
       <c r="K46" s="47"/>
       <c r="L46" s="47"/>
       <c r="M46" s="47"/>
@@ -5133,7 +5087,7 @@
       </c>
       <c r="H47" s="43"/>
       <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
+      <c r="J47" s="54"/>
       <c r="K47" s="47"/>
       <c r="L47" s="47"/>
       <c r="M47" s="47"/>
@@ -5192,7 +5146,7 @@
       </c>
       <c r="H48" s="43"/>
       <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
+      <c r="J48" s="54"/>
       <c r="K48" s="47"/>
       <c r="L48" s="47"/>
       <c r="M48" s="47"/>
@@ -5251,7 +5205,7 @@
       </c>
       <c r="H49" s="43"/>
       <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
+      <c r="J49" s="54"/>
       <c r="K49" s="47"/>
       <c r="L49" s="47"/>
       <c r="M49" s="47"/>
@@ -5310,7 +5264,7 @@
       </c>
       <c r="H50" s="43"/>
       <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
+      <c r="J50" s="54"/>
       <c r="K50" s="47"/>
       <c r="L50" s="47"/>
       <c r="M50" s="47"/>
@@ -5369,7 +5323,7 @@
       </c>
       <c r="H51" s="43"/>
       <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
+      <c r="J51" s="54"/>
       <c r="K51" s="47"/>
       <c r="L51" s="47"/>
       <c r="M51" s="47"/>
@@ -5428,7 +5382,7 @@
       </c>
       <c r="H52" s="43"/>
       <c r="I52" s="43"/>
-      <c r="J52" s="43"/>
+      <c r="J52" s="54"/>
       <c r="K52" s="47"/>
       <c r="L52" s="47"/>
       <c r="M52" s="47"/>
@@ -5487,7 +5441,7 @@
       </c>
       <c r="H53" s="43"/>
       <c r="I53" s="43"/>
-      <c r="J53" s="43"/>
+      <c r="J53" s="54"/>
       <c r="K53" s="47"/>
       <c r="L53" s="47"/>
       <c r="M53" s="47"/>
@@ -5546,7 +5500,7 @@
       </c>
       <c r="H54" s="43"/>
       <c r="I54" s="43"/>
-      <c r="J54" s="43"/>
+      <c r="J54" s="54"/>
       <c r="K54" s="47"/>
       <c r="L54" s="47"/>
       <c r="M54" s="47"/>
@@ -5605,7 +5559,7 @@
       </c>
       <c r="H55" s="43"/>
       <c r="I55" s="43"/>
-      <c r="J55" s="43"/>
+      <c r="J55" s="54"/>
       <c r="K55" s="47"/>
       <c r="L55" s="47"/>
       <c r="M55" s="47"/>
@@ -5664,7 +5618,7 @@
       </c>
       <c r="H56" s="43"/>
       <c r="I56" s="43"/>
-      <c r="J56" s="43"/>
+      <c r="J56" s="54"/>
       <c r="K56" s="47"/>
       <c r="L56" s="47"/>
       <c r="M56" s="47"/>
@@ -5723,7 +5677,7 @@
       </c>
       <c r="H57" s="43"/>
       <c r="I57" s="43"/>
-      <c r="J57" s="43"/>
+      <c r="J57" s="54"/>
       <c r="K57" s="47"/>
       <c r="L57" s="47"/>
       <c r="M57" s="47"/>
@@ -5782,7 +5736,7 @@
       </c>
       <c r="H58" s="43"/>
       <c r="I58" s="43"/>
-      <c r="J58" s="43"/>
+      <c r="J58" s="54"/>
       <c r="K58" s="47"/>
       <c r="L58" s="47"/>
       <c r="M58" s="47"/>
@@ -5841,7 +5795,7 @@
       </c>
       <c r="H59" s="43"/>
       <c r="I59" s="43"/>
-      <c r="J59" s="43"/>
+      <c r="J59" s="54"/>
       <c r="K59" s="47"/>
       <c r="L59" s="47"/>
       <c r="M59" s="47"/>
@@ -5900,7 +5854,7 @@
       </c>
       <c r="H60" s="43"/>
       <c r="I60" s="43"/>
-      <c r="J60" s="43"/>
+      <c r="J60" s="54"/>
       <c r="K60" s="47"/>
       <c r="L60" s="47"/>
       <c r="M60" s="47"/>
@@ -5959,7 +5913,7 @@
       </c>
       <c r="H61" s="43"/>
       <c r="I61" s="43"/>
-      <c r="J61" s="43"/>
+      <c r="J61" s="54"/>
       <c r="K61" s="47"/>
       <c r="L61" s="47"/>
       <c r="M61" s="47"/>
@@ -6018,7 +5972,7 @@
       </c>
       <c r="H62" s="43"/>
       <c r="I62" s="43"/>
-      <c r="J62" s="43"/>
+      <c r="J62" s="54"/>
       <c r="K62" s="47"/>
       <c r="L62" s="47"/>
       <c r="M62" s="47"/>
@@ -6077,7 +6031,7 @@
       </c>
       <c r="H63" s="43"/>
       <c r="I63" s="43"/>
-      <c r="J63" s="43"/>
+      <c r="J63" s="54"/>
       <c r="K63" s="47"/>
       <c r="L63" s="47"/>
       <c r="M63" s="47"/>
@@ -6136,7 +6090,7 @@
       </c>
       <c r="H64" s="43"/>
       <c r="I64" s="43"/>
-      <c r="J64" s="43"/>
+      <c r="J64" s="54"/>
       <c r="K64" s="47"/>
       <c r="L64" s="47"/>
       <c r="M64" s="47"/>
@@ -6195,7 +6149,7 @@
       </c>
       <c r="H65" s="43"/>
       <c r="I65" s="43"/>
-      <c r="J65" s="43"/>
+      <c r="J65" s="54"/>
       <c r="K65" s="47"/>
       <c r="L65" s="47"/>
       <c r="M65" s="47"/>
@@ -6254,7 +6208,7 @@
       </c>
       <c r="H66" s="44"/>
       <c r="I66" s="44"/>
-      <c r="J66" s="44"/>
+      <c r="J66" s="54"/>
       <c r="K66" s="48"/>
       <c r="L66" s="48"/>
       <c r="M66" s="48"/>
@@ -6313,7 +6267,7 @@
       </c>
       <c r="H67" s="44"/>
       <c r="I67" s="44"/>
-      <c r="J67" s="44"/>
+      <c r="J67" s="54"/>
       <c r="K67" s="48"/>
       <c r="L67" s="48"/>
       <c r="M67" s="48"/>
@@ -6372,7 +6326,7 @@
       </c>
       <c r="H68" s="44"/>
       <c r="I68" s="44"/>
-      <c r="J68" s="44"/>
+      <c r="J68" s="54"/>
       <c r="K68" s="48"/>
       <c r="L68" s="48"/>
       <c r="M68" s="48"/>
@@ -6431,7 +6385,7 @@
       </c>
       <c r="H69" s="44"/>
       <c r="I69" s="44"/>
-      <c r="J69" s="44"/>
+      <c r="J69" s="54"/>
       <c r="K69" s="48"/>
       <c r="L69" s="48"/>
       <c r="M69" s="48"/>
@@ -6490,7 +6444,7 @@
       </c>
       <c r="H70" s="44"/>
       <c r="I70" s="44"/>
-      <c r="J70" s="44"/>
+      <c r="J70" s="54"/>
       <c r="K70" s="48"/>
       <c r="L70" s="48"/>
       <c r="M70" s="48"/>
@@ -6549,7 +6503,7 @@
       </c>
       <c r="H71" s="44"/>
       <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
+      <c r="J71" s="54"/>
       <c r="K71" s="48"/>
       <c r="L71" s="48"/>
       <c r="M71" s="48"/>
@@ -6608,7 +6562,7 @@
       </c>
       <c r="H72" s="44"/>
       <c r="I72" s="44"/>
-      <c r="J72" s="44"/>
+      <c r="J72" s="54"/>
       <c r="K72" s="48"/>
       <c r="L72" s="48"/>
       <c r="M72" s="48"/>
@@ -6667,7 +6621,7 @@
       </c>
       <c r="H73" s="44"/>
       <c r="I73" s="44"/>
-      <c r="J73" s="44"/>
+      <c r="J73" s="54"/>
       <c r="K73" s="48"/>
       <c r="L73" s="48"/>
       <c r="M73" s="48"/>
@@ -6726,7 +6680,7 @@
       </c>
       <c r="H74" s="44"/>
       <c r="I74" s="44"/>
-      <c r="J74" s="44"/>
+      <c r="J74" s="54"/>
       <c r="K74" s="48"/>
       <c r="L74" s="48"/>
       <c r="M74" s="48"/>
@@ -6785,7 +6739,7 @@
       </c>
       <c r="H75" s="44"/>
       <c r="I75" s="44"/>
-      <c r="J75" s="44"/>
+      <c r="J75" s="54"/>
       <c r="K75" s="48"/>
       <c r="L75" s="48"/>
       <c r="M75" s="48"/>
@@ -6844,7 +6798,7 @@
       </c>
       <c r="H76" s="44"/>
       <c r="I76" s="44"/>
-      <c r="J76" s="44"/>
+      <c r="J76" s="54"/>
       <c r="K76" s="48"/>
       <c r="L76" s="48"/>
       <c r="M76" s="48"/>
@@ -6903,7 +6857,7 @@
       </c>
       <c r="H77" s="44"/>
       <c r="I77" s="44"/>
-      <c r="J77" s="44"/>
+      <c r="J77" s="54"/>
       <c r="K77" s="48"/>
       <c r="L77" s="48"/>
       <c r="M77" s="48"/>
@@ -6962,7 +6916,7 @@
       </c>
       <c r="H78" s="44"/>
       <c r="I78" s="44"/>
-      <c r="J78" s="44"/>
+      <c r="J78" s="54"/>
       <c r="K78" s="48"/>
       <c r="L78" s="48"/>
       <c r="M78" s="48"/>
@@ -7021,7 +6975,7 @@
       </c>
       <c r="H79" s="44"/>
       <c r="I79" s="44"/>
-      <c r="J79" s="44"/>
+      <c r="J79" s="54"/>
       <c r="K79" s="48"/>
       <c r="L79" s="48"/>
       <c r="M79" s="48"/>
@@ -7080,7 +7034,7 @@
       </c>
       <c r="H80" s="44"/>
       <c r="I80" s="44"/>
-      <c r="J80" s="44"/>
+      <c r="J80" s="54"/>
       <c r="K80" s="48"/>
       <c r="L80" s="48"/>
       <c r="M80" s="48"/>
@@ -7139,7 +7093,7 @@
       </c>
       <c r="H81" s="44"/>
       <c r="I81" s="44"/>
-      <c r="J81" s="44"/>
+      <c r="J81" s="54"/>
       <c r="K81" s="48"/>
       <c r="L81" s="48"/>
       <c r="M81" s="48"/>
@@ -7198,7 +7152,7 @@
       </c>
       <c r="H82" s="44"/>
       <c r="I82" s="44"/>
-      <c r="J82" s="44"/>
+      <c r="J82" s="54"/>
       <c r="K82" s="48"/>
       <c r="L82" s="48"/>
       <c r="M82" s="48"/>
@@ -7257,7 +7211,7 @@
       </c>
       <c r="H83" s="44"/>
       <c r="I83" s="44"/>
-      <c r="J83" s="44"/>
+      <c r="J83" s="54"/>
       <c r="K83" s="48"/>
       <c r="L83" s="48"/>
       <c r="M83" s="48"/>
@@ -7316,7 +7270,7 @@
       </c>
       <c r="H84" s="44"/>
       <c r="I84" s="44"/>
-      <c r="J84" s="44"/>
+      <c r="J84" s="54"/>
       <c r="K84" s="48"/>
       <c r="L84" s="48"/>
       <c r="M84" s="48"/>
@@ -7375,7 +7329,7 @@
       </c>
       <c r="H85" s="44"/>
       <c r="I85" s="44"/>
-      <c r="J85" s="44"/>
+      <c r="J85" s="54"/>
       <c r="K85" s="48"/>
       <c r="L85" s="48"/>
       <c r="M85" s="48"/>
@@ -7434,7 +7388,7 @@
       </c>
       <c r="H86" s="44"/>
       <c r="I86" s="44"/>
-      <c r="J86" s="44"/>
+      <c r="J86" s="54"/>
       <c r="K86" s="48"/>
       <c r="L86" s="48"/>
       <c r="M86" s="48"/>
@@ -7493,7 +7447,7 @@
       </c>
       <c r="H87" s="44"/>
       <c r="I87" s="44"/>
-      <c r="J87" s="44"/>
+      <c r="J87" s="54"/>
       <c r="K87" s="48"/>
       <c r="L87" s="48"/>
       <c r="M87" s="48"/>
@@ -7552,7 +7506,7 @@
       </c>
       <c r="H88" s="44"/>
       <c r="I88" s="44"/>
-      <c r="J88" s="44"/>
+      <c r="J88" s="54"/>
       <c r="K88" s="48"/>
       <c r="L88" s="48"/>
       <c r="M88" s="48"/>
@@ -7611,7 +7565,7 @@
       </c>
       <c r="H89" s="44"/>
       <c r="I89" s="44"/>
-      <c r="J89" s="44"/>
+      <c r="J89" s="54"/>
       <c r="K89" s="48"/>
       <c r="L89" s="48"/>
       <c r="M89" s="48"/>
@@ -7670,7 +7624,7 @@
       </c>
       <c r="H90" s="44"/>
       <c r="I90" s="44"/>
-      <c r="J90" s="44"/>
+      <c r="J90" s="54"/>
       <c r="K90" s="48"/>
       <c r="L90" s="48"/>
       <c r="M90" s="48"/>
@@ -7729,7 +7683,7 @@
       </c>
       <c r="H91" s="44"/>
       <c r="I91" s="44"/>
-      <c r="J91" s="44"/>
+      <c r="J91" s="54"/>
       <c r="K91" s="48"/>
       <c r="L91" s="48"/>
       <c r="M91" s="48"/>
@@ -7788,7 +7742,7 @@
       </c>
       <c r="H92" s="44"/>
       <c r="I92" s="44"/>
-      <c r="J92" s="44"/>
+      <c r="J92" s="54"/>
       <c r="K92" s="48"/>
       <c r="L92" s="48"/>
       <c r="M92" s="48"/>
@@ -7847,7 +7801,7 @@
       </c>
       <c r="H93" s="44"/>
       <c r="I93" s="44"/>
-      <c r="J93" s="44"/>
+      <c r="J93" s="54"/>
       <c r="K93" s="48"/>
       <c r="L93" s="48"/>
       <c r="M93" s="48"/>
@@ -7906,7 +7860,7 @@
       </c>
       <c r="H94" s="44"/>
       <c r="I94" s="44"/>
-      <c r="J94" s="44"/>
+      <c r="J94" s="54"/>
       <c r="K94" s="48"/>
       <c r="L94" s="48"/>
       <c r="M94" s="48"/>
@@ -7965,7 +7919,7 @@
       </c>
       <c r="H95" s="44"/>
       <c r="I95" s="44"/>
-      <c r="J95" s="44"/>
+      <c r="J95" s="54"/>
       <c r="K95" s="48"/>
       <c r="L95" s="48"/>
       <c r="M95" s="48"/>
@@ -8024,7 +7978,7 @@
       </c>
       <c r="H96" s="44"/>
       <c r="I96" s="44"/>
-      <c r="J96" s="44"/>
+      <c r="J96" s="54"/>
       <c r="K96" s="48"/>
       <c r="L96" s="48"/>
       <c r="M96" s="48"/>
@@ -8083,7 +8037,7 @@
       </c>
       <c r="H97" s="44"/>
       <c r="I97" s="44"/>
-      <c r="J97" s="44"/>
+      <c r="J97" s="54"/>
       <c r="K97" s="48"/>
       <c r="L97" s="48"/>
       <c r="M97" s="48"/>
@@ -8142,7 +8096,7 @@
       </c>
       <c r="H98" s="44"/>
       <c r="I98" s="44"/>
-      <c r="J98" s="44"/>
+      <c r="J98" s="54"/>
       <c r="K98" s="48"/>
       <c r="L98" s="48"/>
       <c r="M98" s="48"/>
@@ -8201,7 +8155,7 @@
       </c>
       <c r="H99" s="44"/>
       <c r="I99" s="44"/>
-      <c r="J99" s="44"/>
+      <c r="J99" s="54"/>
       <c r="K99" s="48"/>
       <c r="L99" s="48"/>
       <c r="M99" s="48"/>
@@ -8260,7 +8214,7 @@
       </c>
       <c r="H100" s="44"/>
       <c r="I100" s="44"/>
-      <c r="J100" s="44"/>
+      <c r="J100" s="54"/>
       <c r="K100" s="48"/>
       <c r="L100" s="48"/>
       <c r="M100" s="48"/>
@@ -8319,7 +8273,7 @@
       </c>
       <c r="H101" s="44"/>
       <c r="I101" s="44"/>
-      <c r="J101" s="44"/>
+      <c r="J101" s="54"/>
       <c r="K101" s="48"/>
       <c r="L101" s="48"/>
       <c r="M101" s="48"/>
@@ -8378,7 +8332,7 @@
       </c>
       <c r="H102" s="44"/>
       <c r="I102" s="44"/>
-      <c r="J102" s="44"/>
+      <c r="J102" s="54"/>
       <c r="K102" s="48"/>
       <c r="L102" s="48"/>
       <c r="M102" s="48"/>
@@ -8437,7 +8391,7 @@
       </c>
       <c r="H103" s="44"/>
       <c r="I103" s="44"/>
-      <c r="J103" s="44"/>
+      <c r="J103" s="54"/>
       <c r="K103" s="48"/>
       <c r="L103" s="48"/>
       <c r="M103" s="48"/>
@@ -8496,7 +8450,7 @@
       </c>
       <c r="H104" s="44"/>
       <c r="I104" s="44"/>
-      <c r="J104" s="44"/>
+      <c r="J104" s="54"/>
       <c r="K104" s="48"/>
       <c r="L104" s="48"/>
       <c r="M104" s="48"/>
@@ -8555,7 +8509,7 @@
       </c>
       <c r="H105" s="44"/>
       <c r="I105" s="44"/>
-      <c r="J105" s="44"/>
+      <c r="J105" s="54"/>
       <c r="K105" s="48"/>
       <c r="L105" s="48"/>
       <c r="M105" s="48"/>
@@ -8614,7 +8568,7 @@
       </c>
       <c r="H106" s="44"/>
       <c r="I106" s="44"/>
-      <c r="J106" s="44"/>
+      <c r="J106" s="54"/>
       <c r="K106" s="48"/>
       <c r="L106" s="48"/>
       <c r="M106" s="48"/>
@@ -8673,7 +8627,7 @@
       </c>
       <c r="H107" s="44"/>
       <c r="I107" s="44"/>
-      <c r="J107" s="44"/>
+      <c r="J107" s="54"/>
       <c r="K107" s="48"/>
       <c r="L107" s="48"/>
       <c r="M107" s="48"/>
@@ -8732,7 +8686,7 @@
       </c>
       <c r="H108" s="44"/>
       <c r="I108" s="44"/>
-      <c r="J108" s="44"/>
+      <c r="J108" s="54"/>
       <c r="K108" s="48"/>
       <c r="L108" s="48"/>
       <c r="M108" s="48"/>
@@ -8791,7 +8745,7 @@
       </c>
       <c r="H109" s="44"/>
       <c r="I109" s="44"/>
-      <c r="J109" s="44"/>
+      <c r="J109" s="54"/>
       <c r="K109" s="48"/>
       <c r="L109" s="48"/>
       <c r="M109" s="48"/>
@@ -8850,7 +8804,7 @@
       </c>
       <c r="H110" s="44"/>
       <c r="I110" s="44"/>
-      <c r="J110" s="44"/>
+      <c r="J110" s="54"/>
       <c r="K110" s="48"/>
       <c r="L110" s="48"/>
       <c r="M110" s="48"/>
@@ -8909,7 +8863,7 @@
       </c>
       <c r="H111" s="44"/>
       <c r="I111" s="44"/>
-      <c r="J111" s="44"/>
+      <c r="J111" s="54"/>
       <c r="K111" s="48"/>
       <c r="L111" s="48"/>
       <c r="M111" s="48"/>
@@ -8968,7 +8922,7 @@
       </c>
       <c r="H112" s="44"/>
       <c r="I112" s="44"/>
-      <c r="J112" s="44"/>
+      <c r="J112" s="54"/>
       <c r="K112" s="48"/>
       <c r="L112" s="48"/>
       <c r="M112" s="48"/>
@@ -9027,7 +8981,7 @@
       </c>
       <c r="H113" s="44"/>
       <c r="I113" s="44"/>
-      <c r="J113" s="44"/>
+      <c r="J113" s="54"/>
       <c r="K113" s="48"/>
       <c r="L113" s="48"/>
       <c r="M113" s="48"/>
@@ -9086,7 +9040,7 @@
       </c>
       <c r="H114" s="44"/>
       <c r="I114" s="44"/>
-      <c r="J114" s="44"/>
+      <c r="J114" s="54"/>
       <c r="K114" s="48"/>
       <c r="L114" s="48"/>
       <c r="M114" s="48"/>
@@ -9145,7 +9099,7 @@
       </c>
       <c r="H115" s="44"/>
       <c r="I115" s="44"/>
-      <c r="J115" s="44"/>
+      <c r="J115" s="54"/>
       <c r="K115" s="48"/>
       <c r="L115" s="48"/>
       <c r="M115" s="48"/>
@@ -9204,7 +9158,7 @@
       </c>
       <c r="H116" s="44"/>
       <c r="I116" s="44"/>
-      <c r="J116" s="44"/>
+      <c r="J116" s="54"/>
       <c r="K116" s="48"/>
       <c r="L116" s="48"/>
       <c r="M116" s="48"/>
@@ -9263,7 +9217,7 @@
       </c>
       <c r="H117" s="44"/>
       <c r="I117" s="44"/>
-      <c r="J117" s="44"/>
+      <c r="J117" s="54"/>
       <c r="K117" s="48"/>
       <c r="L117" s="48"/>
       <c r="M117" s="48"/>
@@ -9322,7 +9276,7 @@
       </c>
       <c r="H118" s="44"/>
       <c r="I118" s="44"/>
-      <c r="J118" s="44"/>
+      <c r="J118" s="54"/>
       <c r="K118" s="48"/>
       <c r="L118" s="48"/>
       <c r="M118" s="48"/>
@@ -9381,7 +9335,7 @@
       </c>
       <c r="H119" s="44"/>
       <c r="I119" s="44"/>
-      <c r="J119" s="44"/>
+      <c r="J119" s="54"/>
       <c r="K119" s="48"/>
       <c r="L119" s="48"/>
       <c r="M119" s="48"/>
@@ -9440,7 +9394,7 @@
       </c>
       <c r="H120" s="44"/>
       <c r="I120" s="44"/>
-      <c r="J120" s="44"/>
+      <c r="J120" s="54"/>
       <c r="K120" s="48"/>
       <c r="L120" s="48"/>
       <c r="M120" s="48"/>
@@ -9499,7 +9453,7 @@
       </c>
       <c r="H121" s="44"/>
       <c r="I121" s="44"/>
-      <c r="J121" s="44"/>
+      <c r="J121" s="54"/>
       <c r="K121" s="48"/>
       <c r="L121" s="48"/>
       <c r="M121" s="48"/>
@@ -9558,7 +9512,7 @@
       </c>
       <c r="H122" s="44"/>
       <c r="I122" s="44"/>
-      <c r="J122" s="44"/>
+      <c r="J122" s="54"/>
       <c r="K122" s="48"/>
       <c r="L122" s="48"/>
       <c r="M122" s="48"/>
@@ -9617,7 +9571,7 @@
       </c>
       <c r="H123" s="44"/>
       <c r="I123" s="44"/>
-      <c r="J123" s="44"/>
+      <c r="J123" s="54"/>
       <c r="K123" s="48"/>
       <c r="L123" s="48"/>
       <c r="M123" s="48"/>
@@ -9676,7 +9630,7 @@
       </c>
       <c r="H124" s="44"/>
       <c r="I124" s="44"/>
-      <c r="J124" s="44"/>
+      <c r="J124" s="54"/>
       <c r="K124" s="48"/>
       <c r="L124" s="48"/>
       <c r="M124" s="48"/>
@@ -9735,7 +9689,7 @@
       </c>
       <c r="H125" s="44"/>
       <c r="I125" s="44"/>
-      <c r="J125" s="44"/>
+      <c r="J125" s="54"/>
       <c r="K125" s="48"/>
       <c r="L125" s="48"/>
       <c r="M125" s="48"/>
@@ -9794,7 +9748,7 @@
       </c>
       <c r="H126" s="44"/>
       <c r="I126" s="44"/>
-      <c r="J126" s="44"/>
+      <c r="J126" s="54"/>
       <c r="K126" s="48"/>
       <c r="L126" s="48"/>
       <c r="M126" s="48"/>
@@ -9853,7 +9807,7 @@
       </c>
       <c r="H127" s="44"/>
       <c r="I127" s="44"/>
-      <c r="J127" s="44"/>
+      <c r="J127" s="54"/>
       <c r="K127" s="48"/>
       <c r="L127" s="48"/>
       <c r="M127" s="48"/>
@@ -9912,7 +9866,7 @@
       </c>
       <c r="H128" s="44"/>
       <c r="I128" s="44"/>
-      <c r="J128" s="44"/>
+      <c r="J128" s="54"/>
       <c r="K128" s="48"/>
       <c r="L128" s="48"/>
       <c r="M128" s="48"/>
@@ -9971,7 +9925,7 @@
       </c>
       <c r="H129" s="44"/>
       <c r="I129" s="44"/>
-      <c r="J129" s="44"/>
+      <c r="J129" s="54"/>
       <c r="K129" s="48"/>
       <c r="L129" s="48"/>
       <c r="M129" s="48"/>
@@ -10030,7 +9984,7 @@
       </c>
       <c r="H130" s="44"/>
       <c r="I130" s="44"/>
-      <c r="J130" s="44"/>
+      <c r="J130" s="54"/>
       <c r="K130" s="48"/>
       <c r="L130" s="48"/>
       <c r="M130" s="48"/>
@@ -10089,7 +10043,7 @@
       </c>
       <c r="H131" s="44"/>
       <c r="I131" s="44"/>
-      <c r="J131" s="44"/>
+      <c r="J131" s="54"/>
       <c r="K131" s="48"/>
       <c r="L131" s="48"/>
       <c r="M131" s="48"/>
@@ -10148,7 +10102,7 @@
       </c>
       <c r="H132" s="44"/>
       <c r="I132" s="44"/>
-      <c r="J132" s="44"/>
+      <c r="J132" s="54"/>
       <c r="K132" s="48"/>
       <c r="L132" s="48"/>
       <c r="M132" s="48"/>
@@ -10207,7 +10161,7 @@
       </c>
       <c r="H133" s="44"/>
       <c r="I133" s="44"/>
-      <c r="J133" s="44"/>
+      <c r="J133" s="54"/>
       <c r="K133" s="48"/>
       <c r="L133" s="48"/>
       <c r="M133" s="48"/>
@@ -10266,7 +10220,7 @@
       </c>
       <c r="H134" s="44"/>
       <c r="I134" s="44"/>
-      <c r="J134" s="44"/>
+      <c r="J134" s="54"/>
       <c r="K134" s="48"/>
       <c r="L134" s="48"/>
       <c r="M134" s="48"/>
@@ -10325,7 +10279,7 @@
       </c>
       <c r="H135" s="44"/>
       <c r="I135" s="44"/>
-      <c r="J135" s="44"/>
+      <c r="J135" s="54"/>
       <c r="K135" s="48"/>
       <c r="L135" s="48"/>
       <c r="M135" s="48"/>
@@ -10384,7 +10338,7 @@
       </c>
       <c r="H136" s="44"/>
       <c r="I136" s="44"/>
-      <c r="J136" s="44"/>
+      <c r="J136" s="54"/>
       <c r="K136" s="48"/>
       <c r="L136" s="48"/>
       <c r="M136" s="48"/>
@@ -10443,7 +10397,7 @@
       </c>
       <c r="H137" s="44"/>
       <c r="I137" s="44"/>
-      <c r="J137" s="44"/>
+      <c r="J137" s="54"/>
       <c r="K137" s="48"/>
       <c r="L137" s="48"/>
       <c r="M137" s="48"/>
@@ -10502,7 +10456,7 @@
       </c>
       <c r="H138" s="44"/>
       <c r="I138" s="44"/>
-      <c r="J138" s="44"/>
+      <c r="J138" s="54"/>
       <c r="K138" s="48"/>
       <c r="L138" s="48"/>
       <c r="M138" s="48"/>
@@ -10561,7 +10515,7 @@
       </c>
       <c r="H139" s="44"/>
       <c r="I139" s="44"/>
-      <c r="J139" s="44"/>
+      <c r="J139" s="54"/>
       <c r="K139" s="48"/>
       <c r="L139" s="48"/>
       <c r="M139" s="48"/>
@@ -10620,7 +10574,7 @@
       </c>
       <c r="H140" s="44"/>
       <c r="I140" s="44"/>
-      <c r="J140" s="44"/>
+      <c r="J140" s="54"/>
       <c r="K140" s="48"/>
       <c r="L140" s="48"/>
       <c r="M140" s="48"/>
@@ -10679,7 +10633,7 @@
       </c>
       <c r="H141" s="44"/>
       <c r="I141" s="44"/>
-      <c r="J141" s="44"/>
+      <c r="J141" s="54"/>
       <c r="K141" s="48"/>
       <c r="L141" s="48"/>
       <c r="M141" s="48"/>
@@ -10738,7 +10692,7 @@
       </c>
       <c r="H142" s="44"/>
       <c r="I142" s="44"/>
-      <c r="J142" s="44"/>
+      <c r="J142" s="54"/>
       <c r="K142" s="48"/>
       <c r="L142" s="48"/>
       <c r="M142" s="48"/>
@@ -10797,7 +10751,7 @@
       </c>
       <c r="H143" s="44"/>
       <c r="I143" s="44"/>
-      <c r="J143" s="44"/>
+      <c r="J143" s="54"/>
       <c r="K143" s="48"/>
       <c r="L143" s="48"/>
       <c r="M143" s="48"/>
@@ -10856,7 +10810,7 @@
       </c>
       <c r="H144" s="44"/>
       <c r="I144" s="44"/>
-      <c r="J144" s="44"/>
+      <c r="J144" s="54"/>
       <c r="K144" s="48"/>
       <c r="L144" s="48"/>
       <c r="M144" s="48"/>
@@ -10915,7 +10869,7 @@
       </c>
       <c r="H145" s="44"/>
       <c r="I145" s="44"/>
-      <c r="J145" s="44"/>
+      <c r="J145" s="54"/>
       <c r="K145" s="48"/>
       <c r="L145" s="48"/>
       <c r="M145" s="48"/>
@@ -10974,7 +10928,7 @@
       </c>
       <c r="H146" s="44"/>
       <c r="I146" s="44"/>
-      <c r="J146" s="44"/>
+      <c r="J146" s="54"/>
       <c r="K146" s="48"/>
       <c r="L146" s="48"/>
       <c r="M146" s="48"/>
@@ -11033,7 +10987,7 @@
       </c>
       <c r="H147" s="44"/>
       <c r="I147" s="44"/>
-      <c r="J147" s="44"/>
+      <c r="J147" s="54"/>
       <c r="K147" s="48"/>
       <c r="L147" s="48"/>
       <c r="M147" s="48"/>
@@ -11092,7 +11046,7 @@
       </c>
       <c r="H148" s="44"/>
       <c r="I148" s="44"/>
-      <c r="J148" s="44"/>
+      <c r="J148" s="54"/>
       <c r="K148" s="48"/>
       <c r="L148" s="48"/>
       <c r="M148" s="48"/>
@@ -11151,7 +11105,7 @@
       </c>
       <c r="H149" s="44"/>
       <c r="I149" s="44"/>
-      <c r="J149" s="44"/>
+      <c r="J149" s="54"/>
       <c r="K149" s="48"/>
       <c r="L149" s="48"/>
       <c r="M149" s="48"/>
@@ -11210,7 +11164,7 @@
       </c>
       <c r="H150" s="44"/>
       <c r="I150" s="44"/>
-      <c r="J150" s="44"/>
+      <c r="J150" s="54"/>
       <c r="K150" s="48"/>
       <c r="L150" s="48"/>
       <c r="M150" s="48"/>
@@ -11269,7 +11223,7 @@
       </c>
       <c r="H151" s="44"/>
       <c r="I151" s="44"/>
-      <c r="J151" s="44"/>
+      <c r="J151" s="54"/>
       <c r="K151" s="48"/>
       <c r="L151" s="48"/>
       <c r="M151" s="48"/>
@@ -11328,7 +11282,7 @@
       </c>
       <c r="H152" s="44"/>
       <c r="I152" s="44"/>
-      <c r="J152" s="44"/>
+      <c r="J152" s="54"/>
       <c r="K152" s="48"/>
       <c r="L152" s="48"/>
       <c r="M152" s="48"/>
@@ -11387,7 +11341,7 @@
       </c>
       <c r="H153" s="44"/>
       <c r="I153" s="44"/>
-      <c r="J153" s="44"/>
+      <c r="J153" s="54"/>
       <c r="K153" s="48"/>
       <c r="L153" s="48"/>
       <c r="M153" s="48"/>
@@ -11446,7 +11400,7 @@
       </c>
       <c r="H154" s="44"/>
       <c r="I154" s="44"/>
-      <c r="J154" s="44"/>
+      <c r="J154" s="54"/>
       <c r="K154" s="48"/>
       <c r="L154" s="48"/>
       <c r="M154" s="48"/>
@@ -11505,7 +11459,7 @@
       </c>
       <c r="H155" s="44"/>
       <c r="I155" s="44"/>
-      <c r="J155" s="44"/>
+      <c r="J155" s="54"/>
       <c r="K155" s="48"/>
       <c r="L155" s="48"/>
       <c r="M155" s="48"/>
@@ -11564,7 +11518,7 @@
       </c>
       <c r="H156" s="44"/>
       <c r="I156" s="44"/>
-      <c r="J156" s="44"/>
+      <c r="J156" s="54"/>
       <c r="K156" s="48"/>
       <c r="L156" s="48"/>
       <c r="M156" s="48"/>
@@ -11623,7 +11577,7 @@
       </c>
       <c r="H157" s="44"/>
       <c r="I157" s="44"/>
-      <c r="J157" s="44"/>
+      <c r="J157" s="54"/>
       <c r="K157" s="48"/>
       <c r="L157" s="48"/>
       <c r="M157" s="48"/>
@@ -11682,7 +11636,7 @@
       </c>
       <c r="H158" s="44"/>
       <c r="I158" s="44"/>
-      <c r="J158" s="44"/>
+      <c r="J158" s="54"/>
       <c r="K158" s="48"/>
       <c r="L158" s="48"/>
       <c r="M158" s="48"/>
@@ -11741,7 +11695,7 @@
       </c>
       <c r="H159" s="44"/>
       <c r="I159" s="44"/>
-      <c r="J159" s="44"/>
+      <c r="J159" s="54"/>
       <c r="K159" s="48"/>
       <c r="L159" s="48"/>
       <c r="M159" s="48"/>
@@ -11800,7 +11754,7 @@
       </c>
       <c r="H160" s="44"/>
       <c r="I160" s="44"/>
-      <c r="J160" s="44"/>
+      <c r="J160" s="54"/>
       <c r="K160" s="48"/>
       <c r="L160" s="48"/>
       <c r="M160" s="48"/>
@@ -11859,7 +11813,7 @@
       </c>
       <c r="H161" s="44"/>
       <c r="I161" s="44"/>
-      <c r="J161" s="44"/>
+      <c r="J161" s="54"/>
       <c r="K161" s="48"/>
       <c r="L161" s="48"/>
       <c r="M161" s="48"/>
@@ -11918,7 +11872,7 @@
       </c>
       <c r="H162" s="44"/>
       <c r="I162" s="44"/>
-      <c r="J162" s="44"/>
+      <c r="J162" s="54"/>
       <c r="K162" s="48"/>
       <c r="L162" s="48"/>
       <c r="M162" s="48"/>
@@ -11977,7 +11931,7 @@
       </c>
       <c r="H163" s="44"/>
       <c r="I163" s="44"/>
-      <c r="J163" s="44"/>
+      <c r="J163" s="54"/>
       <c r="K163" s="48"/>
       <c r="L163" s="48"/>
       <c r="M163" s="48"/>
@@ -12036,7 +11990,7 @@
       </c>
       <c r="H164" s="44"/>
       <c r="I164" s="44"/>
-      <c r="J164" s="44"/>
+      <c r="J164" s="54"/>
       <c r="K164" s="48"/>
       <c r="L164" s="48"/>
       <c r="M164" s="48"/>
@@ -12095,7 +12049,7 @@
       </c>
       <c r="H165" s="44"/>
       <c r="I165" s="44"/>
-      <c r="J165" s="44"/>
+      <c r="J165" s="54"/>
       <c r="K165" s="48"/>
       <c r="L165" s="48"/>
       <c r="M165" s="48"/>
@@ -12154,7 +12108,7 @@
       </c>
       <c r="H166" s="44"/>
       <c r="I166" s="44"/>
-      <c r="J166" s="44"/>
+      <c r="J166" s="54"/>
       <c r="K166" s="48"/>
       <c r="L166" s="48"/>
       <c r="M166" s="48"/>
@@ -12213,7 +12167,7 @@
       </c>
       <c r="H167" s="44"/>
       <c r="I167" s="44"/>
-      <c r="J167" s="44"/>
+      <c r="J167" s="54"/>
       <c r="K167" s="48"/>
       <c r="L167" s="48"/>
       <c r="M167" s="48"/>
@@ -12272,7 +12226,7 @@
       </c>
       <c r="H168" s="44"/>
       <c r="I168" s="44"/>
-      <c r="J168" s="44"/>
+      <c r="J168" s="54"/>
       <c r="K168" s="48"/>
       <c r="L168" s="48"/>
       <c r="M168" s="48"/>
@@ -12331,7 +12285,7 @@
       </c>
       <c r="H169" s="44"/>
       <c r="I169" s="44"/>
-      <c r="J169" s="44"/>
+      <c r="J169" s="54"/>
       <c r="K169" s="48"/>
       <c r="L169" s="48"/>
       <c r="M169" s="48"/>
@@ -12390,7 +12344,7 @@
       </c>
       <c r="H170" s="44"/>
       <c r="I170" s="44"/>
-      <c r="J170" s="44"/>
+      <c r="J170" s="54"/>
       <c r="K170" s="48"/>
       <c r="L170" s="48"/>
       <c r="M170" s="48"/>
@@ -12449,7 +12403,7 @@
       </c>
       <c r="H171" s="44"/>
       <c r="I171" s="44"/>
-      <c r="J171" s="44"/>
+      <c r="J171" s="54"/>
       <c r="K171" s="48"/>
       <c r="L171" s="48"/>
       <c r="M171" s="48"/>
@@ -12508,7 +12462,7 @@
       </c>
       <c r="H172" s="44"/>
       <c r="I172" s="44"/>
-      <c r="J172" s="44"/>
+      <c r="J172" s="54"/>
       <c r="K172" s="48"/>
       <c r="L172" s="48"/>
       <c r="M172" s="48"/>
@@ -12567,7 +12521,7 @@
       </c>
       <c r="H173" s="44"/>
       <c r="I173" s="44"/>
-      <c r="J173" s="44"/>
+      <c r="J173" s="54"/>
       <c r="K173" s="48"/>
       <c r="L173" s="48"/>
       <c r="M173" s="48"/>
@@ -12626,7 +12580,7 @@
       </c>
       <c r="H174" s="44"/>
       <c r="I174" s="44"/>
-      <c r="J174" s="44"/>
+      <c r="J174" s="54"/>
       <c r="K174" s="48"/>
       <c r="L174" s="48"/>
       <c r="M174" s="48"/>
@@ -12685,7 +12639,7 @@
       </c>
       <c r="H175" s="44"/>
       <c r="I175" s="44"/>
-      <c r="J175" s="44"/>
+      <c r="J175" s="54"/>
       <c r="K175" s="48"/>
       <c r="L175" s="48"/>
       <c r="M175" s="48"/>
@@ -12744,7 +12698,7 @@
       </c>
       <c r="H176" s="44"/>
       <c r="I176" s="44"/>
-      <c r="J176" s="44"/>
+      <c r="J176" s="54"/>
       <c r="K176" s="48"/>
       <c r="L176" s="48"/>
       <c r="M176" s="48"/>
@@ -12803,7 +12757,7 @@
       </c>
       <c r="H177" s="44"/>
       <c r="I177" s="44"/>
-      <c r="J177" s="44"/>
+      <c r="J177" s="54"/>
       <c r="K177" s="48"/>
       <c r="L177" s="48"/>
       <c r="M177" s="48"/>
@@ -12862,7 +12816,7 @@
       </c>
       <c r="H178" s="44"/>
       <c r="I178" s="44"/>
-      <c r="J178" s="44"/>
+      <c r="J178" s="54"/>
       <c r="K178" s="48"/>
       <c r="L178" s="48"/>
       <c r="M178" s="48"/>
@@ -12921,7 +12875,7 @@
       </c>
       <c r="H179" s="44"/>
       <c r="I179" s="44"/>
-      <c r="J179" s="44"/>
+      <c r="J179" s="54"/>
       <c r="K179" s="48"/>
       <c r="L179" s="48"/>
       <c r="M179" s="48"/>
@@ -12980,7 +12934,7 @@
       </c>
       <c r="H180" s="44"/>
       <c r="I180" s="44"/>
-      <c r="J180" s="44"/>
+      <c r="J180" s="54"/>
       <c r="K180" s="48"/>
       <c r="L180" s="48"/>
       <c r="M180" s="48"/>
@@ -13039,7 +12993,7 @@
       </c>
       <c r="H181" s="44"/>
       <c r="I181" s="44"/>
-      <c r="J181" s="44"/>
+      <c r="J181" s="54"/>
       <c r="K181" s="48"/>
       <c r="L181" s="48"/>
       <c r="M181" s="48"/>
@@ -13098,7 +13052,7 @@
       </c>
       <c r="H182" s="44"/>
       <c r="I182" s="44"/>
-      <c r="J182" s="44"/>
+      <c r="J182" s="54"/>
       <c r="K182" s="48"/>
       <c r="L182" s="48"/>
       <c r="M182" s="48"/>
@@ -13157,7 +13111,7 @@
       </c>
       <c r="H183" s="44"/>
       <c r="I183" s="44"/>
-      <c r="J183" s="44"/>
+      <c r="J183" s="54"/>
       <c r="K183" s="48"/>
       <c r="L183" s="48"/>
       <c r="M183" s="48"/>
@@ -13216,7 +13170,7 @@
       </c>
       <c r="H184" s="44"/>
       <c r="I184" s="44"/>
-      <c r="J184" s="44"/>
+      <c r="J184" s="54"/>
       <c r="K184" s="48"/>
       <c r="L184" s="48"/>
       <c r="M184" s="48"/>
@@ -13275,7 +13229,7 @@
       </c>
       <c r="H185" s="44"/>
       <c r="I185" s="44"/>
-      <c r="J185" s="44"/>
+      <c r="J185" s="54"/>
       <c r="K185" s="48"/>
       <c r="L185" s="48"/>
       <c r="M185" s="48"/>
@@ -13334,7 +13288,7 @@
       </c>
       <c r="H186" s="44"/>
       <c r="I186" s="44"/>
-      <c r="J186" s="44"/>
+      <c r="J186" s="54"/>
       <c r="K186" s="48"/>
       <c r="L186" s="48"/>
       <c r="M186" s="48"/>
@@ -13393,7 +13347,7 @@
       </c>
       <c r="H187" s="44"/>
       <c r="I187" s="44"/>
-      <c r="J187" s="44"/>
+      <c r="J187" s="54"/>
       <c r="K187" s="48"/>
       <c r="L187" s="48"/>
       <c r="M187" s="48"/>
@@ -13452,7 +13406,7 @@
       </c>
       <c r="H188" s="44"/>
       <c r="I188" s="44"/>
-      <c r="J188" s="44"/>
+      <c r="J188" s="54"/>
       <c r="K188" s="48"/>
       <c r="L188" s="48"/>
       <c r="M188" s="48"/>
@@ -13511,7 +13465,7 @@
       </c>
       <c r="H189" s="44"/>
       <c r="I189" s="44"/>
-      <c r="J189" s="44"/>
+      <c r="J189" s="54"/>
       <c r="K189" s="48"/>
       <c r="L189" s="48"/>
       <c r="M189" s="48"/>
@@ -13570,7 +13524,7 @@
       </c>
       <c r="H190" s="44"/>
       <c r="I190" s="44"/>
-      <c r="J190" s="44"/>
+      <c r="J190" s="54"/>
       <c r="K190" s="48"/>
       <c r="L190" s="48"/>
       <c r="M190" s="48"/>
@@ -13629,7 +13583,7 @@
       </c>
       <c r="H191" s="44"/>
       <c r="I191" s="44"/>
-      <c r="J191" s="44"/>
+      <c r="J191" s="54"/>
       <c r="K191" s="48"/>
       <c r="L191" s="48"/>
       <c r="M191" s="48"/>
@@ -13688,7 +13642,7 @@
       </c>
       <c r="H192" s="44"/>
       <c r="I192" s="44"/>
-      <c r="J192" s="44"/>
+      <c r="J192" s="54"/>
       <c r="K192" s="48"/>
       <c r="L192" s="48"/>
       <c r="M192" s="48"/>
@@ -13747,7 +13701,7 @@
       </c>
       <c r="H193" s="44"/>
       <c r="I193" s="44"/>
-      <c r="J193" s="44"/>
+      <c r="J193" s="54"/>
       <c r="K193" s="48"/>
       <c r="L193" s="48"/>
       <c r="M193" s="48"/>
@@ -13806,7 +13760,7 @@
       </c>
       <c r="H194" s="44"/>
       <c r="I194" s="44"/>
-      <c r="J194" s="44"/>
+      <c r="J194" s="54"/>
       <c r="K194" s="48"/>
       <c r="L194" s="48"/>
       <c r="M194" s="48"/>
@@ -13865,7 +13819,7 @@
       </c>
       <c r="H195" s="44"/>
       <c r="I195" s="44"/>
-      <c r="J195" s="44"/>
+      <c r="J195" s="54"/>
       <c r="K195" s="48"/>
       <c r="L195" s="48"/>
       <c r="M195" s="48"/>
@@ -13924,7 +13878,7 @@
       </c>
       <c r="H196" s="44"/>
       <c r="I196" s="44"/>
-      <c r="J196" s="44"/>
+      <c r="J196" s="54"/>
       <c r="K196" s="48"/>
       <c r="L196" s="48"/>
       <c r="M196" s="48"/>
@@ -13983,7 +13937,7 @@
       </c>
       <c r="H197" s="44"/>
       <c r="I197" s="44"/>
-      <c r="J197" s="44"/>
+      <c r="J197" s="54"/>
       <c r="K197" s="48"/>
       <c r="L197" s="48"/>
       <c r="M197" s="48"/>
@@ -14042,7 +13996,7 @@
       </c>
       <c r="H198" s="44"/>
       <c r="I198" s="44"/>
-      <c r="J198" s="44"/>
+      <c r="J198" s="54"/>
       <c r="K198" s="48"/>
       <c r="L198" s="48"/>
       <c r="M198" s="48"/>
@@ -14101,7 +14055,7 @@
       </c>
       <c r="H199" s="44"/>
       <c r="I199" s="44"/>
-      <c r="J199" s="44"/>
+      <c r="J199" s="54"/>
       <c r="K199" s="48"/>
       <c r="L199" s="48"/>
       <c r="M199" s="48"/>
@@ -14160,7 +14114,7 @@
       </c>
       <c r="H200" s="44"/>
       <c r="I200" s="44"/>
-      <c r="J200" s="44"/>
+      <c r="J200" s="54"/>
       <c r="K200" s="48"/>
       <c r="L200" s="48"/>
       <c r="M200" s="48"/>
@@ -14219,7 +14173,7 @@
       </c>
       <c r="H201" s="44"/>
       <c r="I201" s="44"/>
-      <c r="J201" s="44"/>
+      <c r="J201" s="54"/>
       <c r="K201" s="48"/>
       <c r="L201" s="48"/>
       <c r="M201" s="48"/>
@@ -14278,7 +14232,7 @@
       </c>
       <c r="H202" s="44"/>
       <c r="I202" s="44"/>
-      <c r="J202" s="44"/>
+      <c r="J202" s="54"/>
       <c r="K202" s="48"/>
       <c r="L202" s="48"/>
       <c r="M202" s="48"/>
@@ -14337,7 +14291,7 @@
       </c>
       <c r="H203" s="44"/>
       <c r="I203" s="44"/>
-      <c r="J203" s="44"/>
+      <c r="J203" s="54"/>
       <c r="K203" s="48"/>
       <c r="L203" s="48"/>
       <c r="M203" s="48"/>
@@ -14396,7 +14350,7 @@
       </c>
       <c r="H204" s="44"/>
       <c r="I204" s="44"/>
-      <c r="J204" s="44"/>
+      <c r="J204" s="54"/>
       <c r="K204" s="48"/>
       <c r="L204" s="48"/>
       <c r="M204" s="48"/>
@@ -14455,7 +14409,7 @@
       </c>
       <c r="H205" s="66"/>
       <c r="I205" s="66"/>
-      <c r="J205" s="66"/>
+      <c r="J205" s="54"/>
       <c r="K205" s="69"/>
       <c r="L205" s="69"/>
       <c r="M205" s="69"/>
@@ -14525,14 +14479,14 @@
     <dataValidation type="list" sqref="I6:I205" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Consulta,Pré-reserva,Confirmada,Concluída,Cancelada"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J6:J205" xr:uid="{00000000-0002-0000-0200-000002000000}">
-      <formula1>"Direto,Airbnb,Booking,Imobiliária,Indicação,Outro"</formula1>
-    </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DATA DE ENTRADA INDISPONÍVEL" error="Esta data coincide ou está dentro de outra reserva, inclusive no dia de saída. Escolha outra data." promptTitle="Entrada da reserva" prompt="Escolha uma data livre. Dias já comprometidos, inclusive check-out de outra reserva, são bloqueados." sqref="C6:C205" xr:uid="{00000000-0002-0000-0200-000006000000}">
       <formula1>OR(C6="",SUMPRODUCT(($C$6:$C$205&lt;=C6)*($D$6:$D$205&gt;=C6)*($I$6:$I$205&lt;&gt;"Cancelada")*($I$6:$I$205&lt;&gt;"Consulta")*(ROW($C$6:$C$205)&lt;&gt;ROW()))=0)</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="PERÍODO INDISPONÍVEL" error="A saída deve ser posterior à entrada e o período inteiro precisa estar livre, sem coincidir com outra reserva." promptTitle="Saída da reserva" prompt="Informe uma saída posterior à entrada. O período não pode sobrepor nenhuma reserva existente." sqref="D6:D205" xr:uid="{00000000-0002-0000-0200-000007000000}">
       <formula1>OR(D6="",AND(C6&lt;&gt;"",D6&gt;C6,SUMPRODUCT(($C$6:$C$205&lt;=D6)*($D$6:$D$205&gt;=C6)*($I$6:$I$205&lt;&gt;"Cancelada")*($I$6:$I$205&lt;&gt;"Consulta")*(ROW($C$6:$C$205)&lt;&gt;ROW()))=0))</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J6:J205" xr:uid="{B22C96CE-7948-45F7-BCA7-CAA02DD8F23B}">
+      <formula1>"Direto,Airbnb,Booking,Imobiliária,Indicação,Cortesia,Outro"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14553,24 +14507,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
     </row>
     <row r="3" spans="1:6" ht="27.15" customHeight="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="94" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
     </row>
     <row r="5" spans="1:6" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -17047,12 +17001,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -17167,7 +17121,7 @@
         <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -17179,6 +17133,9 @@
       </c>
       <c r="D10" t="s">
         <v>109</v>
+      </c>
+      <c r="F10" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6">
